--- a/output/roomself_excel/5509.xlsx
+++ b/output/roomself_excel/5509.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,16 +470,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>493069</v>
+        <v>301983</v>
       </c>
       <c r="D2" t="n">
-        <v>9333</v>
+        <v>6128</v>
       </c>
       <c r="E2" t="n">
-        <v>1016</v>
+        <v>892</v>
       </c>
       <c r="F2" t="n">
-        <v>892</v>
+        <v>599</v>
       </c>
     </row>
     <row r="3">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>59302</v>
+        <v>83844</v>
       </c>
       <c r="D4" t="n">
-        <v>1988</v>
+        <v>2320</v>
       </c>
       <c r="E4" t="n">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="F4" t="n">
-        <v>232</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>48720</v>
+        <v>109962</v>
       </c>
       <c r="D5" t="n">
-        <v>1924</v>
+        <v>2668</v>
       </c>
       <c r="E5" t="n">
-        <v>248</v>
+        <v>402</v>
       </c>
       <c r="F5" t="n">
-        <v>160</v>
+        <v>331</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>194214</v>
+        <v>107876</v>
       </c>
       <c r="D6" t="n">
-        <v>5211</v>
+        <v>2640</v>
       </c>
       <c r="E6" t="n">
-        <v>1035</v>
+        <v>395</v>
       </c>
       <c r="F6" t="n">
-        <v>809</v>
+        <v>331</v>
       </c>
     </row>
     <row r="7">
@@ -580,16 +580,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20967</v>
+        <v>48720</v>
       </c>
       <c r="D7" t="n">
-        <v>1244</v>
+        <v>1924</v>
       </c>
       <c r="E7" t="n">
-        <v>126</v>
+        <v>248</v>
       </c>
       <c r="F7" t="n">
-        <v>19</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>88707</v>
+        <v>20967</v>
       </c>
       <c r="D8" t="n">
-        <v>2908</v>
+        <v>1244</v>
       </c>
       <c r="E8" t="n">
-        <v>803</v>
+        <v>126</v>
       </c>
       <c r="F8" t="n">
-        <v>580</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>37380</v>
+        <v>32148</v>
       </c>
       <c r="D9" t="n">
-        <v>1652</v>
+        <v>1436</v>
       </c>
       <c r="E9" t="n">
-        <v>448</v>
+        <v>224</v>
       </c>
       <c r="F9" t="n">
-        <v>366</v>
+        <v>202</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>83844</v>
+        <v>194214</v>
       </c>
       <c r="D10" t="n">
-        <v>2320</v>
+        <v>5211</v>
       </c>
       <c r="E10" t="n">
-        <v>540</v>
+        <v>809</v>
       </c>
       <c r="F10" t="n">
-        <v>91</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>109962</v>
+        <v>67706</v>
       </c>
       <c r="D11" t="n">
-        <v>2668</v>
+        <v>2454</v>
       </c>
       <c r="E11" t="n">
-        <v>402</v>
+        <v>177</v>
       </c>
       <c r="F11" t="n">
-        <v>331</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>107876</v>
+        <v>59302</v>
       </c>
       <c r="D12" t="n">
-        <v>2640</v>
+        <v>1988</v>
       </c>
       <c r="E12" t="n">
-        <v>395</v>
+        <v>331</v>
       </c>
       <c r="F12" t="n">
-        <v>331</v>
+        <v>232</v>
       </c>
     </row>
     <row r="13">
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>32148</v>
+        <v>123380</v>
       </c>
       <c r="D13" t="n">
-        <v>1436</v>
+        <v>2983</v>
       </c>
       <c r="E13" t="n">
-        <v>224</v>
+        <v>344</v>
       </c>
       <c r="F13" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="14">
@@ -734,15 +734,59 @@
         </is>
       </c>
       <c r="C14" t="n">
+        <v>88707</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2908</v>
+      </c>
+      <c r="E14" t="n">
+        <v>112</v>
+      </c>
+      <c r="F14" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>37380</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1652</v>
+      </c>
+      <c r="E15" t="n">
+        <v>153</v>
+      </c>
+      <c r="F15" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
         <v>64128</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D16" t="n">
         <v>2104</v>
       </c>
-      <c r="E14" t="n">
-        <v>803</v>
-      </c>
-      <c r="F14" t="n">
+      <c r="E16" t="n">
+        <v>456</v>
+      </c>
+      <c r="F16" t="n">
         <v>219</v>
       </c>
     </row>

--- a/output/roomself_excel/5509.xlsx
+++ b/output/roomself_excel/5509.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,11 +495,27 @@
       <c r="D2" t="n">
         <v>6128</v>
       </c>
-      <c r="E2" t="n">
-        <v>892</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>599</v>
+        <v>509</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>1007</v>
+      </c>
+      <c r="J2" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="3">
@@ -497,11 +533,27 @@
       <c r="D3" t="n">
         <v>3304</v>
       </c>
-      <c r="E3" t="n">
-        <v>561</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>331</v>
+        <v>514</v>
+      </c>
+      <c r="G3" t="n">
+        <v>33</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>298</v>
+      </c>
+      <c r="J3" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="4">
@@ -519,12 +571,20 @@
       <c r="D4" t="n">
         <v>2320</v>
       </c>
-      <c r="E4" t="n">
-        <v>337</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>60</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="G4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,11 +601,27 @@
       <c r="D5" t="n">
         <v>2668</v>
       </c>
-      <c r="E5" t="n">
-        <v>402</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>331</v>
+        <v>298</v>
+      </c>
+      <c r="G5" t="n">
+        <v>33</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>369</v>
+      </c>
+      <c r="J5" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="6">
@@ -563,11 +639,27 @@
       <c r="D6" t="n">
         <v>2640</v>
       </c>
-      <c r="E6" t="n">
-        <v>395</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>331</v>
+        <v>287</v>
+      </c>
+      <c r="G6" t="n">
+        <v>33</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>362</v>
+      </c>
+      <c r="J6" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="7">
@@ -585,12 +677,20 @@
       <c r="D7" t="n">
         <v>1924</v>
       </c>
-      <c r="E7" t="n">
-        <v>248</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>160</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="G7" t="n">
+        <v>33</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +707,20 @@
       <c r="D8" t="n">
         <v>1244</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>126</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>19</v>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,11 +737,27 @@
       <c r="D9" t="n">
         <v>1436</v>
       </c>
-      <c r="E9" t="n">
-        <v>224</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>202</v>
+        <v>171</v>
+      </c>
+      <c r="G9" t="n">
+        <v>36</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>188</v>
+      </c>
+      <c r="J9" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="10">
@@ -651,12 +775,20 @@
       <c r="D10" t="n">
         <v>5211</v>
       </c>
-      <c r="E10" t="n">
-        <v>809</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>342</v>
-      </c>
+        <v>523</v>
+      </c>
+      <c r="G10" t="n">
+        <v>33</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +805,20 @@
       <c r="D11" t="n">
         <v>2454</v>
       </c>
-      <c r="E11" t="n">
-        <v>177</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>145</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="G11" t="n">
+        <v>19</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,11 +835,27 @@
       <c r="D12" t="n">
         <v>1988</v>
       </c>
-      <c r="E12" t="n">
-        <v>331</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>232</v>
+        <v>186</v>
+      </c>
+      <c r="G12" t="n">
+        <v>33</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>287</v>
+      </c>
+      <c r="J12" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="13">
@@ -717,11 +873,27 @@
       <c r="D13" t="n">
         <v>2983</v>
       </c>
-      <c r="E13" t="n">
-        <v>344</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>204</v>
+        <v>173</v>
+      </c>
+      <c r="G13" t="n">
+        <v>30</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>279</v>
+      </c>
+      <c r="J13" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -739,12 +911,20 @@
       <c r="D14" t="n">
         <v>2908</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
         <v>112</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>31</v>
       </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,10 +941,26 @@
       <c r="D15" t="n">
         <v>1652</v>
       </c>
-      <c r="E15" t="n">
-        <v>153</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F15" t="n">
+        <v>20</v>
+      </c>
+      <c r="G15" t="n">
+        <v>19</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>99</v>
+      </c>
+      <c r="J15" t="n">
         <v>31</v>
       </c>
     </row>
@@ -783,11 +979,27 @@
       <c r="D16" t="n">
         <v>2104</v>
       </c>
-      <c r="E16" t="n">
-        <v>456</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F16" t="n">
-        <v>219</v>
+        <v>352</v>
+      </c>
+      <c r="G16" t="n">
+        <v>31</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>334</v>
+      </c>
+      <c r="J16" t="n">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
